--- a/server/excel/release/fusion-temple.xlsx
+++ b/server/excel/release/fusion-temple.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="融合神殿难度" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="融合神殿关卡" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="融合神殿挑战要求" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="融合神殿挑战奖励" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="融合神殿自选奖励" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="融合神殿排行榜" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="融合神殿难度" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="融合神殿关卡" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="融合神殿挑战要求" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="融合神殿挑战奖励" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="融合神殿自选奖励" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="融合神殿排行榜" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="847">
   <si>
     <t xml:space="preserve">难度ID</t>
   </si>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">*说明一下检测操作</t>
   </si>
   <si>
-    <t xml:space="preserve">Chiến đấu thắng lợi</t>
+    <t xml:space="preserve">Thắng trận</t>
   </si>
   <si>
     <t xml:space="preserve">与任务要求的数据</t>
   </si>
   <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1nhân&gt; Tướng</t>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Tân Binh&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">相满足</t>
   </si>
   <si>
-    <t xml:space="preserve">Không được với trận &lt;2214 Trợ &gt; Tướng</t>
+    <t xml:space="preserve">Không ra trận tướng &lt;2214 Buff&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">0：检测值=目标值</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">1：检测值&lt;=目标值</t>
   </si>
   <si>
-    <t xml:space="preserve">Thời gian chiến đấu không cao hơn &lt;2214 5&gt; Hiệp</t>
+    <t xml:space="preserve">Thắng trong vòng &lt;2214 5&gt; hiệp</t>
   </si>
   <si>
     <t xml:space="preserve">2：检测值&gt;=目标值</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhất định phải lên trận tướng</t>
+    <t xml:space="preserve">Phải ra trận &lt;2214 Jinbe&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">什么时候会用到1呢？</t>
@@ -1202,52 +1202,70 @@
     <t xml:space="preserve">比如3回合内通关</t>
   </si>
   <si>
-    <t xml:space="preserve">Bổn tràng chiến đấu không đồng đội tử vong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thắng lợi lúc tất cả tướng huyết lượng tại &lt;2214 20%&gt; Trở lên</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Thần&gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không được với trận tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Ma&gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Chiến &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sử dụng &lt;2214 Phụclongtrận &gt; Đạt được thắng lợi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2Tank &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không được với trận &lt;2214 Tank &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sử dụng &lt;2214 Linhxàtrận &gt; Đạt được thắng lợi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2Thần&gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thắng lợi lúc tất cả tướng huyết lượng tại &lt;2214 30%&gt; Trở lên</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thời gian chiến đấu không cao hơn &lt;2214 7&gt; Hiệp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1nhân &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2yêu &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Pháp sư &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
+    <t xml:space="preserve">Không có đồng đội tử trận</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi thắng, mọi tướng còn từ &lt;2214 20%&gt; HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Hải Quân&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không ra trận &lt;2214 Magellan&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phải ra trận &lt;2214 Tashigi&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Ngũ Hoàng&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Dame&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng bằng trận hình &lt;2214 Lục&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Tank&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không ra trận tướng &lt;2214 Tank&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng bằng trận hình &lt;2214 Vàng&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phải ra trận &lt;2214 Smoker&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phải ra trận &lt;2214 S.Usopp&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Hải Quân&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phải ra trận &lt;2214 Zephyr&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi thắng, mọi tướng còn từ &lt;2214 30%&gt; HP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng trong vòng &lt;2214 7&gt; hiệp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phải ra trận &lt;2214 Ace&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Dũng Sĩ&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phải ra trận &lt;2214 Brook&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Magic&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không ra trận &lt;2214 Marco&gt;, &lt;2214 Ivankov&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">501300#500600</t>
@@ -12243,7 +12261,7 @@
         <v>503</v>
       </c>
       <c r="B16" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C16" t="n">
         <v>105</v>
@@ -12281,7 +12299,7 @@
         <v>602</v>
       </c>
       <c r="B18" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C18" t="n">
         <v>104</v>
@@ -12301,7 +12319,7 @@
         <v>603</v>
       </c>
       <c r="B19" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C19" t="n">
         <v>103</v>
@@ -12339,7 +12357,7 @@
         <v>702</v>
       </c>
       <c r="B21" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C21" t="n">
         <v>102</v>
@@ -12359,7 +12377,7 @@
         <v>703</v>
       </c>
       <c r="B22" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C22" t="n">
         <v>103</v>
@@ -12451,7 +12469,7 @@
         <v>902</v>
       </c>
       <c r="B27" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C27" t="n">
         <v>103</v>
@@ -12471,7 +12489,7 @@
         <v>903</v>
       </c>
       <c r="B28" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C28" t="n">
         <v>102</v>
@@ -12527,7 +12545,7 @@
         <v>1003</v>
       </c>
       <c r="B31" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C31" t="n">
         <v>105</v>
@@ -12585,7 +12603,7 @@
         <v>1103</v>
       </c>
       <c r="B34" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C34" t="n">
         <v>105</v>
@@ -12623,7 +12641,7 @@
         <v>1202</v>
       </c>
       <c r="B36" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C36" t="n">
         <v>104</v>
@@ -12679,7 +12697,7 @@
         <v>1302</v>
       </c>
       <c r="B39" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="C39" t="n">
         <v>105</v>
@@ -12699,7 +12717,7 @@
         <v>1303</v>
       </c>
       <c r="B40" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C40" t="n">
         <v>201</v>
@@ -12735,7 +12753,7 @@
         <v>1402</v>
       </c>
       <c r="B42" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C42" t="n">
         <v>101</v>
@@ -12753,7 +12771,7 @@
         <v>1403</v>
       </c>
       <c r="B43" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C43" t="n">
         <v>104</v>
@@ -12791,7 +12809,7 @@
         <v>1502</v>
       </c>
       <c r="B45" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C45" t="n">
         <v>201</v>
@@ -12809,7 +12827,7 @@
         <v>1503</v>
       </c>
       <c r="B46" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="C46" t="n">
         <v>105</v>
@@ -12865,7 +12883,7 @@
         <v>1603</v>
       </c>
       <c r="B49" t="s">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="C49" t="n">
         <v>104</v>
@@ -12903,7 +12921,7 @@
         <v>1702</v>
       </c>
       <c r="B51" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C51" t="n">
         <v>104</v>
@@ -12959,7 +12977,7 @@
         <v>1802</v>
       </c>
       <c r="B54" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C54" t="n">
         <v>105</v>
@@ -12979,7 +12997,7 @@
         <v>1803</v>
       </c>
       <c r="B55" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C55" t="n">
         <v>103</v>
@@ -13073,13 +13091,13 @@
         <v>2002</v>
       </c>
       <c r="B60" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C60" t="n">
         <v>106</v>
       </c>
       <c r="D60" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -13093,7 +13111,7 @@
         <v>2003</v>
       </c>
       <c r="B61" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C61" t="n">
         <v>104</v>
@@ -18997,16 +19015,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C1" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="E1"/>
     </row>
@@ -19015,7 +19033,7 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C2" t="n">
         <v>1000</v>
@@ -19030,7 +19048,7 @@
         <v>1002</v>
       </c>
       <c r="B3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -19045,7 +19063,7 @@
         <v>1003</v>
       </c>
       <c r="B4" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C4" t="n">
         <v>1000</v>
@@ -19060,7 +19078,7 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
@@ -19075,7 +19093,7 @@
         <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C6" t="n">
         <v>1000</v>
@@ -19090,7 +19108,7 @@
         <v>1006</v>
       </c>
       <c r="B7" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
         <v>1000</v>
@@ -19105,7 +19123,7 @@
         <v>1007</v>
       </c>
       <c r="B8" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C8" t="n">
         <v>100</v>
@@ -19120,7 +19138,7 @@
         <v>1008</v>
       </c>
       <c r="B9" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C9" t="n">
         <v>100</v>
@@ -19135,7 +19153,7 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C10" t="n">
         <v>1000</v>
@@ -19150,7 +19168,7 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C11" t="n">
         <v>100</v>
@@ -19165,7 +19183,7 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C12" t="n">
         <v>50</v>
@@ -19180,7 +19198,7 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C13" t="n">
         <v>25</v>
@@ -19195,7 +19213,7 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C14" t="n">
         <v>20</v>
@@ -19210,7 +19228,7 @@
         <v>2001</v>
       </c>
       <c r="B15" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C15" t="n">
         <v>1000</v>
@@ -19224,7 +19242,7 @@
         <v>2002</v>
       </c>
       <c r="B16" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C16" t="n">
         <v>120</v>
@@ -19238,7 +19256,7 @@
         <v>2003</v>
       </c>
       <c r="B17" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C17" t="n">
         <v>1000</v>
@@ -19252,7 +19270,7 @@
         <v>2004</v>
       </c>
       <c r="B18" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C18" t="n">
         <v>120</v>
@@ -19266,7 +19284,7 @@
         <v>2005</v>
       </c>
       <c r="B19" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C19" t="n">
         <v>1000</v>
@@ -19280,7 +19298,7 @@
         <v>2006</v>
       </c>
       <c r="B20" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C20" t="n">
         <v>1000</v>
@@ -19294,7 +19312,7 @@
         <v>2007</v>
       </c>
       <c r="B21" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C21" t="n">
         <v>120</v>
@@ -19308,7 +19326,7 @@
         <v>2008</v>
       </c>
       <c r="B22" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C22" t="n">
         <v>120</v>
@@ -19322,7 +19340,7 @@
         <v>2009</v>
       </c>
       <c r="B23" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C23" t="n">
         <v>1000</v>
@@ -19336,7 +19354,7 @@
         <v>2010</v>
       </c>
       <c r="B24" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C24" t="n">
         <v>120</v>
@@ -19350,7 +19368,7 @@
         <v>2011</v>
       </c>
       <c r="B25" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C25" t="n">
         <v>60</v>
@@ -19364,7 +19382,7 @@
         <v>2012</v>
       </c>
       <c r="B26" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C26" t="n">
         <v>30</v>
@@ -19378,7 +19396,7 @@
         <v>2013</v>
       </c>
       <c r="B27" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -19392,7 +19410,7 @@
         <v>3001</v>
       </c>
       <c r="B28" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C28" t="n">
         <v>1000</v>
@@ -19406,7 +19424,7 @@
         <v>3002</v>
       </c>
       <c r="B29" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C29" t="n">
         <v>144</v>
@@ -19420,7 +19438,7 @@
         <v>3003</v>
       </c>
       <c r="B30" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C30" t="n">
         <v>1000</v>
@@ -19434,7 +19452,7 @@
         <v>3004</v>
       </c>
       <c r="B31" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C31" t="n">
         <v>144</v>
@@ -19448,7 +19466,7 @@
         <v>3005</v>
       </c>
       <c r="B32" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C32" t="n">
         <v>1000</v>
@@ -19462,7 +19480,7 @@
         <v>3006</v>
       </c>
       <c r="B33" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C33" t="n">
         <v>1000</v>
@@ -19476,7 +19494,7 @@
         <v>3007</v>
       </c>
       <c r="B34" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C34" t="n">
         <v>144</v>
@@ -19490,7 +19508,7 @@
         <v>3008</v>
       </c>
       <c r="B35" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C35" t="n">
         <v>144</v>
@@ -19504,7 +19522,7 @@
         <v>3009</v>
       </c>
       <c r="B36" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C36" t="n">
         <v>1000</v>
@@ -19518,7 +19536,7 @@
         <v>3010</v>
       </c>
       <c r="B37" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C37" t="n">
         <v>144</v>
@@ -19532,7 +19550,7 @@
         <v>3011</v>
       </c>
       <c r="B38" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C38" t="n">
         <v>72</v>
@@ -19546,7 +19564,7 @@
         <v>3012</v>
       </c>
       <c r="B39" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C39" t="n">
         <v>36</v>
@@ -19560,7 +19578,7 @@
         <v>3013</v>
       </c>
       <c r="B40" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C40" t="n">
         <v>29</v>
@@ -19574,7 +19592,7 @@
         <v>4001</v>
       </c>
       <c r="B41" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C41" t="n">
         <v>1000</v>
@@ -19588,7 +19606,7 @@
         <v>4002</v>
       </c>
       <c r="B42" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C42" t="n">
         <v>173</v>
@@ -19602,7 +19620,7 @@
         <v>4003</v>
       </c>
       <c r="B43" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C43" t="n">
         <v>1000</v>
@@ -19616,7 +19634,7 @@
         <v>4004</v>
       </c>
       <c r="B44" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C44" t="n">
         <v>173</v>
@@ -19630,7 +19648,7 @@
         <v>4005</v>
       </c>
       <c r="B45" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C45" t="n">
         <v>1000</v>
@@ -19644,7 +19662,7 @@
         <v>4006</v>
       </c>
       <c r="B46" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C46" t="n">
         <v>1000</v>
@@ -19658,7 +19676,7 @@
         <v>4007</v>
       </c>
       <c r="B47" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C47" t="n">
         <v>173</v>
@@ -19672,7 +19690,7 @@
         <v>4008</v>
       </c>
       <c r="B48" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C48" t="n">
         <v>173</v>
@@ -19686,7 +19704,7 @@
         <v>4009</v>
       </c>
       <c r="B49" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C49" t="n">
         <v>1000</v>
@@ -19700,7 +19718,7 @@
         <v>4010</v>
       </c>
       <c r="B50" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C50" t="n">
         <v>173</v>
@@ -19714,7 +19732,7 @@
         <v>4011</v>
       </c>
       <c r="B51" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C51" t="n">
         <v>86</v>
@@ -19728,7 +19746,7 @@
         <v>4012</v>
       </c>
       <c r="B52" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C52" t="n">
         <v>43</v>
@@ -19742,7 +19760,7 @@
         <v>4013</v>
       </c>
       <c r="B53" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C53" t="n">
         <v>35</v>
@@ -19756,7 +19774,7 @@
         <v>5001</v>
       </c>
       <c r="B54" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C54" t="n">
         <v>1000</v>
@@ -19770,7 +19788,7 @@
         <v>5002</v>
       </c>
       <c r="B55" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C55" t="n">
         <v>207</v>
@@ -19784,7 +19802,7 @@
         <v>5003</v>
       </c>
       <c r="B56" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C56" t="n">
         <v>1000</v>
@@ -19798,7 +19816,7 @@
         <v>5004</v>
       </c>
       <c r="B57" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C57" t="n">
         <v>207</v>
@@ -19812,7 +19830,7 @@
         <v>5005</v>
       </c>
       <c r="B58" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C58" t="n">
         <v>1000</v>
@@ -19826,7 +19844,7 @@
         <v>5006</v>
       </c>
       <c r="B59" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C59" t="n">
         <v>1000</v>
@@ -19840,7 +19858,7 @@
         <v>5007</v>
       </c>
       <c r="B60" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C60" t="n">
         <v>207</v>
@@ -19854,7 +19872,7 @@
         <v>5008</v>
       </c>
       <c r="B61" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C61" t="n">
         <v>207</v>
@@ -19868,7 +19886,7 @@
         <v>5009</v>
       </c>
       <c r="B62" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C62" t="n">
         <v>1000</v>
@@ -19882,7 +19900,7 @@
         <v>5010</v>
       </c>
       <c r="B63" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C63" t="n">
         <v>207</v>
@@ -19896,7 +19914,7 @@
         <v>5011</v>
       </c>
       <c r="B64" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C64" t="n">
         <v>104</v>
@@ -19910,7 +19928,7 @@
         <v>5012</v>
       </c>
       <c r="B65" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C65" t="n">
         <v>52</v>
@@ -19924,7 +19942,7 @@
         <v>5013</v>
       </c>
       <c r="B66" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C66" t="n">
         <v>41</v>
@@ -19938,7 +19956,7 @@
         <v>6001</v>
       </c>
       <c r="B67" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C67" t="n">
         <v>1000</v>
@@ -19952,7 +19970,7 @@
         <v>6002</v>
       </c>
       <c r="B68" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C68" t="n">
         <v>249</v>
@@ -19966,7 +19984,7 @@
         <v>6003</v>
       </c>
       <c r="B69" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C69" t="n">
         <v>1000</v>
@@ -19980,7 +19998,7 @@
         <v>6004</v>
       </c>
       <c r="B70" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C70" t="n">
         <v>249</v>
@@ -19994,7 +20012,7 @@
         <v>6005</v>
       </c>
       <c r="B71" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C71" t="n">
         <v>1000</v>
@@ -20008,7 +20026,7 @@
         <v>6006</v>
       </c>
       <c r="B72" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C72" t="n">
         <v>1000</v>
@@ -20022,7 +20040,7 @@
         <v>6007</v>
       </c>
       <c r="B73" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C73" t="n">
         <v>249</v>
@@ -20036,7 +20054,7 @@
         <v>6008</v>
       </c>
       <c r="B74" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C74" t="n">
         <v>249</v>
@@ -20050,7 +20068,7 @@
         <v>6009</v>
       </c>
       <c r="B75" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C75" t="n">
         <v>1000</v>
@@ -20064,7 +20082,7 @@
         <v>6010</v>
       </c>
       <c r="B76" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C76" t="n">
         <v>249</v>
@@ -20078,7 +20096,7 @@
         <v>6011</v>
       </c>
       <c r="B77" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C77" t="n">
         <v>124</v>
@@ -20092,7 +20110,7 @@
         <v>6012</v>
       </c>
       <c r="B78" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C78" t="n">
         <v>62</v>
@@ -20106,7 +20124,7 @@
         <v>6013</v>
       </c>
       <c r="B79" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C79" t="n">
         <v>50</v>
@@ -20120,7 +20138,7 @@
         <v>7001</v>
       </c>
       <c r="B80" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C80" t="n">
         <v>1000</v>
@@ -20134,7 +20152,7 @@
         <v>7002</v>
       </c>
       <c r="B81" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C81" t="n">
         <v>299</v>
@@ -20148,7 +20166,7 @@
         <v>7003</v>
       </c>
       <c r="B82" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C82" t="n">
         <v>1000</v>
@@ -20162,7 +20180,7 @@
         <v>7004</v>
       </c>
       <c r="B83" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C83" t="n">
         <v>299</v>
@@ -20176,7 +20194,7 @@
         <v>7005</v>
       </c>
       <c r="B84" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C84" t="n">
         <v>1000</v>
@@ -20190,7 +20208,7 @@
         <v>7006</v>
       </c>
       <c r="B85" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C85" t="n">
         <v>1000</v>
@@ -20204,7 +20222,7 @@
         <v>7007</v>
       </c>
       <c r="B86" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C86" t="n">
         <v>299</v>
@@ -20218,7 +20236,7 @@
         <v>7008</v>
       </c>
       <c r="B87" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C87" t="n">
         <v>299</v>
@@ -20232,7 +20250,7 @@
         <v>7009</v>
       </c>
       <c r="B88" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C88" t="n">
         <v>1000</v>
@@ -20246,7 +20264,7 @@
         <v>7010</v>
       </c>
       <c r="B89" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C89" t="n">
         <v>299</v>
@@ -20260,7 +20278,7 @@
         <v>7011</v>
       </c>
       <c r="B90" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C90" t="n">
         <v>149</v>
@@ -20274,7 +20292,7 @@
         <v>7012</v>
       </c>
       <c r="B91" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C91" t="n">
         <v>75</v>
@@ -20288,7 +20306,7 @@
         <v>7013</v>
       </c>
       <c r="B92" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C92" t="n">
         <v>60</v>
@@ -20302,7 +20320,7 @@
         <v>8001</v>
       </c>
       <c r="B93" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C93" t="n">
         <v>1000</v>
@@ -20316,7 +20334,7 @@
         <v>8002</v>
       </c>
       <c r="B94" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C94" t="n">
         <v>358</v>
@@ -20330,7 +20348,7 @@
         <v>8003</v>
       </c>
       <c r="B95" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C95" t="n">
         <v>1000</v>
@@ -20344,7 +20362,7 @@
         <v>8004</v>
       </c>
       <c r="B96" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C96" t="n">
         <v>358</v>
@@ -20358,7 +20376,7 @@
         <v>8005</v>
       </c>
       <c r="B97" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C97" t="n">
         <v>1000</v>
@@ -20372,7 +20390,7 @@
         <v>8006</v>
       </c>
       <c r="B98" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C98" t="n">
         <v>1000</v>
@@ -20386,7 +20404,7 @@
         <v>8007</v>
       </c>
       <c r="B99" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C99" t="n">
         <v>358</v>
@@ -20400,7 +20418,7 @@
         <v>8008</v>
       </c>
       <c r="B100" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C100" t="n">
         <v>358</v>
@@ -20414,7 +20432,7 @@
         <v>8009</v>
       </c>
       <c r="B101" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C101" t="n">
         <v>1000</v>
@@ -20428,7 +20446,7 @@
         <v>8010</v>
       </c>
       <c r="B102" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C102" t="n">
         <v>358</v>
@@ -20442,7 +20460,7 @@
         <v>8011</v>
       </c>
       <c r="B103" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C103" t="n">
         <v>179</v>
@@ -20456,7 +20474,7 @@
         <v>8012</v>
       </c>
       <c r="B104" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C104" t="n">
         <v>90</v>
@@ -20470,7 +20488,7 @@
         <v>8013</v>
       </c>
       <c r="B105" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C105" t="n">
         <v>72</v>
@@ -20484,7 +20502,7 @@
         <v>9001</v>
       </c>
       <c r="B106" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C106" t="n">
         <v>1000</v>
@@ -20498,7 +20516,7 @@
         <v>9002</v>
       </c>
       <c r="B107" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C107" t="n">
         <v>430</v>
@@ -20512,7 +20530,7 @@
         <v>9003</v>
       </c>
       <c r="B108" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C108" t="n">
         <v>1000</v>
@@ -20526,7 +20544,7 @@
         <v>9004</v>
       </c>
       <c r="B109" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C109" t="n">
         <v>430</v>
@@ -20540,7 +20558,7 @@
         <v>9005</v>
       </c>
       <c r="B110" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C110" t="n">
         <v>1000</v>
@@ -20554,7 +20572,7 @@
         <v>9006</v>
       </c>
       <c r="B111" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C111" t="n">
         <v>1000</v>
@@ -20568,7 +20586,7 @@
         <v>9007</v>
       </c>
       <c r="B112" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C112" t="n">
         <v>430</v>
@@ -20582,7 +20600,7 @@
         <v>9008</v>
       </c>
       <c r="B113" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C113" t="n">
         <v>430</v>
@@ -20596,7 +20614,7 @@
         <v>9009</v>
       </c>
       <c r="B114" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C114" t="n">
         <v>1000</v>
@@ -20610,7 +20628,7 @@
         <v>9010</v>
       </c>
       <c r="B115" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C115" t="n">
         <v>430</v>
@@ -20624,7 +20642,7 @@
         <v>9011</v>
       </c>
       <c r="B116" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C116" t="n">
         <v>215</v>
@@ -20638,7 +20656,7 @@
         <v>9012</v>
       </c>
       <c r="B117" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C117" t="n">
         <v>107</v>
@@ -20652,7 +20670,7 @@
         <v>9013</v>
       </c>
       <c r="B118" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C118" t="n">
         <v>86</v>
@@ -20666,7 +20684,7 @@
         <v>10001</v>
       </c>
       <c r="B119" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C119" t="n">
         <v>1000</v>
@@ -20680,7 +20698,7 @@
         <v>10002</v>
       </c>
       <c r="B120" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C120" t="n">
         <v>516</v>
@@ -20694,7 +20712,7 @@
         <v>10003</v>
       </c>
       <c r="B121" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C121" t="n">
         <v>1000</v>
@@ -20708,7 +20726,7 @@
         <v>10004</v>
       </c>
       <c r="B122" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C122" t="n">
         <v>516</v>
@@ -20722,7 +20740,7 @@
         <v>10005</v>
       </c>
       <c r="B123" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C123" t="n">
         <v>1000</v>
@@ -20736,7 +20754,7 @@
         <v>10006</v>
       </c>
       <c r="B124" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C124" t="n">
         <v>1000</v>
@@ -20750,7 +20768,7 @@
         <v>10007</v>
       </c>
       <c r="B125" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C125" t="n">
         <v>516</v>
@@ -20764,7 +20782,7 @@
         <v>10008</v>
       </c>
       <c r="B126" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C126" t="n">
         <v>516</v>
@@ -20778,7 +20796,7 @@
         <v>10009</v>
       </c>
       <c r="B127" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C127" t="n">
         <v>1000</v>
@@ -20792,7 +20810,7 @@
         <v>10010</v>
       </c>
       <c r="B128" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C128" t="n">
         <v>516</v>
@@ -20806,7 +20824,7 @@
         <v>10011</v>
       </c>
       <c r="B129" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C129" t="n">
         <v>258</v>
@@ -20820,7 +20838,7 @@
         <v>10012</v>
       </c>
       <c r="B130" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C130" t="n">
         <v>129</v>
@@ -20834,7 +20852,7 @@
         <v>10013</v>
       </c>
       <c r="B131" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C131" t="n">
         <v>103</v>
@@ -20848,7 +20866,7 @@
         <v>11001</v>
       </c>
       <c r="B132" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C132" t="n">
         <v>1000</v>
@@ -20862,7 +20880,7 @@
         <v>11002</v>
       </c>
       <c r="B133" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C133" t="n">
         <v>619</v>
@@ -20876,7 +20894,7 @@
         <v>11003</v>
       </c>
       <c r="B134" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C134" t="n">
         <v>1000</v>
@@ -20890,7 +20908,7 @@
         <v>11004</v>
       </c>
       <c r="B135" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C135" t="n">
         <v>619</v>
@@ -20904,7 +20922,7 @@
         <v>11005</v>
       </c>
       <c r="B136" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C136" t="n">
         <v>1000</v>
@@ -20918,7 +20936,7 @@
         <v>11006</v>
       </c>
       <c r="B137" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C137" t="n">
         <v>1000</v>
@@ -20932,7 +20950,7 @@
         <v>11007</v>
       </c>
       <c r="B138" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C138" t="n">
         <v>619</v>
@@ -20946,7 +20964,7 @@
         <v>11008</v>
       </c>
       <c r="B139" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C139" t="n">
         <v>619</v>
@@ -20960,7 +20978,7 @@
         <v>11009</v>
       </c>
       <c r="B140" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C140" t="n">
         <v>1000</v>
@@ -20974,7 +20992,7 @@
         <v>11010</v>
       </c>
       <c r="B141" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C141" t="n">
         <v>619</v>
@@ -20988,7 +21006,7 @@
         <v>11011</v>
       </c>
       <c r="B142" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C142" t="n">
         <v>310</v>
@@ -21002,7 +21020,7 @@
         <v>11012</v>
       </c>
       <c r="B143" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C143" t="n">
         <v>155</v>
@@ -21016,7 +21034,7 @@
         <v>11013</v>
       </c>
       <c r="B144" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C144" t="n">
         <v>124</v>
@@ -21030,7 +21048,7 @@
         <v>12001</v>
       </c>
       <c r="B145" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C145" t="n">
         <v>1000</v>
@@ -21044,7 +21062,7 @@
         <v>12002</v>
       </c>
       <c r="B146" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C146" t="n">
         <v>743</v>
@@ -21058,7 +21076,7 @@
         <v>12003</v>
       </c>
       <c r="B147" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C147" t="n">
         <v>1000</v>
@@ -21072,7 +21090,7 @@
         <v>12004</v>
       </c>
       <c r="B148" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C148" t="n">
         <v>743</v>
@@ -21086,7 +21104,7 @@
         <v>12005</v>
       </c>
       <c r="B149" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C149" t="n">
         <v>1000</v>
@@ -21100,7 +21118,7 @@
         <v>12006</v>
       </c>
       <c r="B150" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C150" t="n">
         <v>1000</v>
@@ -21114,7 +21132,7 @@
         <v>12007</v>
       </c>
       <c r="B151" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C151" t="n">
         <v>743</v>
@@ -21128,7 +21146,7 @@
         <v>12008</v>
       </c>
       <c r="B152" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C152" t="n">
         <v>743</v>
@@ -21142,7 +21160,7 @@
         <v>12009</v>
       </c>
       <c r="B153" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C153" t="n">
         <v>1000</v>
@@ -21156,7 +21174,7 @@
         <v>12010</v>
       </c>
       <c r="B154" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C154" t="n">
         <v>743</v>
@@ -21170,7 +21188,7 @@
         <v>12011</v>
       </c>
       <c r="B155" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C155" t="n">
         <v>372</v>
@@ -21184,7 +21202,7 @@
         <v>12012</v>
       </c>
       <c r="B156" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C156" t="n">
         <v>186</v>
@@ -21198,7 +21216,7 @@
         <v>12013</v>
       </c>
       <c r="B157" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C157" t="n">
         <v>149</v>
@@ -21212,7 +21230,7 @@
         <v>13001</v>
       </c>
       <c r="B158" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C158" t="n">
         <v>1000</v>
@@ -21226,7 +21244,7 @@
         <v>13002</v>
       </c>
       <c r="B159" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C159" t="n">
         <v>892</v>
@@ -21240,7 +21258,7 @@
         <v>13003</v>
       </c>
       <c r="B160" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C160" t="n">
         <v>1000</v>
@@ -21254,7 +21272,7 @@
         <v>13004</v>
       </c>
       <c r="B161" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C161" t="n">
         <v>892</v>
@@ -21268,7 +21286,7 @@
         <v>13005</v>
       </c>
       <c r="B162" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C162" t="n">
         <v>1000</v>
@@ -21282,7 +21300,7 @@
         <v>13006</v>
       </c>
       <c r="B163" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C163" t="n">
         <v>1000</v>
@@ -21296,7 +21314,7 @@
         <v>13007</v>
       </c>
       <c r="B164" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C164" t="n">
         <v>892</v>
@@ -21310,7 +21328,7 @@
         <v>13008</v>
       </c>
       <c r="B165" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C165" t="n">
         <v>892</v>
@@ -21324,7 +21342,7 @@
         <v>13009</v>
       </c>
       <c r="B166" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C166" t="n">
         <v>1000</v>
@@ -21338,7 +21356,7 @@
         <v>13010</v>
       </c>
       <c r="B167" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C167" t="n">
         <v>892</v>
@@ -21352,7 +21370,7 @@
         <v>13011</v>
       </c>
       <c r="B168" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C168" t="n">
         <v>446</v>
@@ -21366,7 +21384,7 @@
         <v>13012</v>
       </c>
       <c r="B169" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C169" t="n">
         <v>223</v>
@@ -21380,7 +21398,7 @@
         <v>13013</v>
       </c>
       <c r="B170" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C170" t="n">
         <v>178</v>
@@ -21394,7 +21412,7 @@
         <v>14001</v>
       </c>
       <c r="B171" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C171" t="n">
         <v>1000</v>
@@ -21408,7 +21426,7 @@
         <v>14002</v>
       </c>
       <c r="B172" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C172" t="n">
         <v>1070</v>
@@ -21422,7 +21440,7 @@
         <v>14003</v>
       </c>
       <c r="B173" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C173" t="n">
         <v>1000</v>
@@ -21436,7 +21454,7 @@
         <v>14004</v>
       </c>
       <c r="B174" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C174" t="n">
         <v>1070</v>
@@ -21450,7 +21468,7 @@
         <v>14005</v>
       </c>
       <c r="B175" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C175" t="n">
         <v>1000</v>
@@ -21464,7 +21482,7 @@
         <v>14006</v>
       </c>
       <c r="B176" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C176" t="n">
         <v>1000</v>
@@ -21478,7 +21496,7 @@
         <v>14007</v>
       </c>
       <c r="B177" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C177" t="n">
         <v>1070</v>
@@ -21492,7 +21510,7 @@
         <v>14008</v>
       </c>
       <c r="B178" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C178" t="n">
         <v>1070</v>
@@ -21506,7 +21524,7 @@
         <v>14009</v>
       </c>
       <c r="B179" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C179" t="n">
         <v>1000</v>
@@ -21520,7 +21538,7 @@
         <v>14010</v>
       </c>
       <c r="B180" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C180" t="n">
         <v>1070</v>
@@ -21534,7 +21552,7 @@
         <v>14011</v>
       </c>
       <c r="B181" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C181" t="n">
         <v>535</v>
@@ -21548,7 +21566,7 @@
         <v>14012</v>
       </c>
       <c r="B182" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C182" t="n">
         <v>267</v>
@@ -21562,7 +21580,7 @@
         <v>14013</v>
       </c>
       <c r="B183" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C183" t="n">
         <v>214</v>
@@ -21576,7 +21594,7 @@
         <v>15001</v>
       </c>
       <c r="B184" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C184" t="n">
         <v>1000</v>
@@ -21590,7 +21608,7 @@
         <v>15002</v>
       </c>
       <c r="B185" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C185" t="n">
         <v>1284</v>
@@ -21604,7 +21622,7 @@
         <v>15003</v>
       </c>
       <c r="B186" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C186" t="n">
         <v>1000</v>
@@ -21618,7 +21636,7 @@
         <v>15004</v>
       </c>
       <c r="B187" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C187" t="n">
         <v>1284</v>
@@ -21632,7 +21650,7 @@
         <v>15005</v>
       </c>
       <c r="B188" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C188" t="n">
         <v>1000</v>
@@ -21646,7 +21664,7 @@
         <v>15006</v>
       </c>
       <c r="B189" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C189" t="n">
         <v>1000</v>
@@ -21660,7 +21678,7 @@
         <v>15007</v>
       </c>
       <c r="B190" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C190" t="n">
         <v>1284</v>
@@ -21674,7 +21692,7 @@
         <v>15008</v>
       </c>
       <c r="B191" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C191" t="n">
         <v>1284</v>
@@ -21688,7 +21706,7 @@
         <v>15009</v>
       </c>
       <c r="B192" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C192" t="n">
         <v>1000</v>
@@ -21702,7 +21720,7 @@
         <v>15010</v>
       </c>
       <c r="B193" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C193" t="n">
         <v>1284</v>
@@ -21716,7 +21734,7 @@
         <v>15011</v>
       </c>
       <c r="B194" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C194" t="n">
         <v>642</v>
@@ -21730,7 +21748,7 @@
         <v>15012</v>
       </c>
       <c r="B195" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C195" t="n">
         <v>321</v>
@@ -21744,7 +21762,7 @@
         <v>15013</v>
       </c>
       <c r="B196" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C196" t="n">
         <v>257</v>
@@ -21769,13 +21787,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
@@ -21786,7 +21804,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
@@ -21797,7 +21815,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4">
@@ -21808,7 +21826,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5">
@@ -21819,7 +21837,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6">
@@ -21830,7 +21848,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7">
@@ -21841,7 +21859,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8">
@@ -21852,7 +21870,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -21863,7 +21881,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10">
@@ -21874,7 +21892,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
@@ -21885,7 +21903,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12">
@@ -21896,7 +21914,7 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13">
@@ -21907,7 +21925,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14">
@@ -21918,7 +21936,7 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F14"/>
     </row>
@@ -21930,7 +21948,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="F15"/>
     </row>
@@ -21942,7 +21960,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F16"/>
     </row>
@@ -21954,7 +21972,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F17"/>
     </row>
@@ -21966,7 +21984,7 @@
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F18"/>
     </row>
@@ -21978,7 +21996,7 @@
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="F19"/>
     </row>
@@ -21990,7 +22008,7 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F20"/>
     </row>
@@ -22002,7 +22020,7 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F21"/>
     </row>
@@ -22014,7 +22032,7 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F22"/>
     </row>
@@ -22026,7 +22044,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F23"/>
     </row>
@@ -22038,7 +22056,7 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F24"/>
     </row>
@@ -22050,7 +22068,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="F25"/>
     </row>
@@ -22062,7 +22080,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F26"/>
     </row>
@@ -22074,7 +22092,7 @@
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F27"/>
     </row>
@@ -22086,7 +22104,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F28"/>
     </row>
@@ -22098,7 +22116,7 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F29"/>
     </row>
@@ -22110,7 +22128,7 @@
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F30"/>
     </row>
@@ -22122,7 +22140,7 @@
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F31"/>
     </row>
@@ -22134,7 +22152,7 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F32"/>
     </row>
@@ -22146,7 +22164,7 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F33"/>
     </row>
@@ -22158,7 +22176,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="F34"/>
     </row>
@@ -22170,7 +22188,7 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F35"/>
     </row>
@@ -22182,7 +22200,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F36"/>
     </row>
@@ -22194,7 +22212,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F37"/>
     </row>
@@ -22206,7 +22224,7 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F38"/>
     </row>
@@ -22218,7 +22236,7 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F39"/>
     </row>
@@ -22230,7 +22248,7 @@
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F40"/>
     </row>
@@ -22242,7 +22260,7 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F41"/>
     </row>
@@ -22254,7 +22272,7 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="F42"/>
     </row>
@@ -22266,7 +22284,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="F43"/>
     </row>
@@ -22278,7 +22296,7 @@
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F44"/>
     </row>
@@ -22290,7 +22308,7 @@
         <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F45"/>
     </row>
@@ -22302,7 +22320,7 @@
         <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F46"/>
     </row>
@@ -22314,7 +22332,7 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F47"/>
     </row>
@@ -22326,7 +22344,7 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F48"/>
     </row>
@@ -22338,7 +22356,7 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F49"/>
     </row>
@@ -22350,7 +22368,7 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F50"/>
     </row>
@@ -22362,7 +22380,7 @@
         <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F51"/>
     </row>
@@ -22374,7 +22392,7 @@
         <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="F52"/>
     </row>
@@ -22386,7 +22404,7 @@
         <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="F53"/>
     </row>
@@ -22398,7 +22416,7 @@
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F54"/>
     </row>
@@ -22410,7 +22428,7 @@
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F55"/>
     </row>
@@ -22422,7 +22440,7 @@
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F56"/>
     </row>
@@ -22434,7 +22452,7 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F57"/>
     </row>
@@ -22446,7 +22464,7 @@
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F58"/>
     </row>
@@ -22458,7 +22476,7 @@
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F59"/>
     </row>
@@ -22470,7 +22488,7 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F60"/>
     </row>
@@ -22482,7 +22500,7 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="F61"/>
     </row>
@@ -22494,7 +22512,7 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="F62"/>
     </row>
@@ -22506,7 +22524,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F63"/>
     </row>
@@ -22518,7 +22536,7 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="F64"/>
     </row>
@@ -22530,7 +22548,7 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F65"/>
     </row>
@@ -22542,7 +22560,7 @@
         <v>8</v>
       </c>
       <c r="C66" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F66"/>
     </row>
@@ -22554,7 +22572,7 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F67"/>
     </row>
@@ -22566,7 +22584,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="F68"/>
     </row>
@@ -22578,7 +22596,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F69"/>
     </row>
@@ -22590,7 +22608,7 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F70"/>
     </row>
@@ -22602,7 +22620,7 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F71"/>
     </row>
@@ -22614,7 +22632,7 @@
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F72"/>
     </row>
@@ -22626,7 +22644,7 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="F73"/>
     </row>
@@ -22638,7 +22656,7 @@
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F74"/>
     </row>
@@ -22650,7 +22668,7 @@
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="F75"/>
     </row>
@@ -22662,7 +22680,7 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F76"/>
     </row>
@@ -22674,7 +22692,7 @@
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F77"/>
     </row>
@@ -22686,7 +22704,7 @@
         <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F78"/>
     </row>
@@ -22698,7 +22716,7 @@
         <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="F79"/>
     </row>
@@ -22710,7 +22728,7 @@
         <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F80"/>
     </row>
@@ -22722,7 +22740,7 @@
         <v>9</v>
       </c>
       <c r="C81" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F81"/>
     </row>
@@ -22734,7 +22752,7 @@
         <v>9</v>
       </c>
       <c r="C82" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F82"/>
     </row>
@@ -22746,7 +22764,7 @@
         <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F83"/>
     </row>
@@ -22758,7 +22776,7 @@
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F84"/>
     </row>
@@ -22770,7 +22788,7 @@
         <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="F85"/>
     </row>
@@ -22782,7 +22800,7 @@
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F86"/>
     </row>
@@ -22794,7 +22812,7 @@
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F87"/>
     </row>
@@ -22806,7 +22824,7 @@
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="F88"/>
     </row>
@@ -22818,7 +22836,7 @@
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F89"/>
     </row>
@@ -22830,7 +22848,7 @@
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F90"/>
     </row>
@@ -22842,7 +22860,7 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F91"/>
     </row>
@@ -22854,7 +22872,7 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F92"/>
     </row>
@@ -22866,7 +22884,7 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F93"/>
     </row>
@@ -22878,7 +22896,7 @@
         <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F94"/>
     </row>
@@ -22890,7 +22908,7 @@
         <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F95"/>
     </row>
@@ -22902,7 +22920,7 @@
         <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F96"/>
     </row>
@@ -22914,7 +22932,7 @@
         <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F97"/>
     </row>
@@ -22926,7 +22944,7 @@
         <v>10</v>
       </c>
       <c r="C98" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="F98"/>
     </row>
@@ -22938,7 +22956,7 @@
         <v>10</v>
       </c>
       <c r="C99" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F99"/>
     </row>
@@ -22950,7 +22968,7 @@
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F100"/>
     </row>
@@ -22962,7 +22980,7 @@
         <v>10</v>
       </c>
       <c r="C101" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="F101"/>
     </row>
@@ -22974,7 +22992,7 @@
         <v>10</v>
       </c>
       <c r="C102" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F102"/>
     </row>
@@ -22986,7 +23004,7 @@
         <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="F103"/>
     </row>
@@ -22998,7 +23016,7 @@
         <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="F104"/>
     </row>
@@ -23010,7 +23028,7 @@
         <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F105"/>
     </row>
@@ -23022,7 +23040,7 @@
         <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F106"/>
     </row>
@@ -23034,7 +23052,7 @@
         <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="F107"/>
     </row>
@@ -23046,7 +23064,7 @@
         <v>11</v>
       </c>
       <c r="C108" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F108"/>
     </row>
@@ -23058,7 +23076,7 @@
         <v>11</v>
       </c>
       <c r="C109" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F109"/>
     </row>
@@ -23070,7 +23088,7 @@
         <v>11</v>
       </c>
       <c r="C110" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="F110"/>
     </row>
@@ -23082,7 +23100,7 @@
         <v>11</v>
       </c>
       <c r="C111" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F111"/>
     </row>
@@ -23094,7 +23112,7 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F112"/>
     </row>
@@ -23106,7 +23124,7 @@
         <v>11</v>
       </c>
       <c r="C113" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F113"/>
     </row>
@@ -23118,7 +23136,7 @@
         <v>11</v>
       </c>
       <c r="C114" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="F114"/>
     </row>
@@ -23130,7 +23148,7 @@
         <v>11</v>
       </c>
       <c r="C115" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F115"/>
     </row>
@@ -23142,7 +23160,7 @@
         <v>11</v>
       </c>
       <c r="C116" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="F116"/>
     </row>
@@ -23154,7 +23172,7 @@
         <v>11</v>
       </c>
       <c r="C117" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="F117"/>
     </row>
@@ -23166,7 +23184,7 @@
         <v>11</v>
       </c>
       <c r="C118" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F118"/>
     </row>
@@ -23178,7 +23196,7 @@
         <v>11</v>
       </c>
       <c r="C119" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="F119"/>
     </row>
@@ -23190,7 +23208,7 @@
         <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="F120"/>
     </row>
@@ -23202,7 +23220,7 @@
         <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="F121"/>
     </row>
@@ -23214,7 +23232,7 @@
         <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F122"/>
     </row>
@@ -23226,7 +23244,7 @@
         <v>12</v>
       </c>
       <c r="C123" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F123"/>
     </row>
@@ -23238,7 +23256,7 @@
         <v>12</v>
       </c>
       <c r="C124" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F124"/>
     </row>
@@ -23250,7 +23268,7 @@
         <v>12</v>
       </c>
       <c r="C125" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F125"/>
     </row>
@@ -23262,7 +23280,7 @@
         <v>12</v>
       </c>
       <c r="C126" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F126"/>
     </row>
@@ -23274,7 +23292,7 @@
         <v>12</v>
       </c>
       <c r="C127" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="F127"/>
     </row>
@@ -23286,7 +23304,7 @@
         <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F128"/>
     </row>
@@ -23298,7 +23316,7 @@
         <v>12</v>
       </c>
       <c r="C129" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F129"/>
     </row>
@@ -23310,7 +23328,7 @@
         <v>12</v>
       </c>
       <c r="C130" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F130"/>
     </row>
@@ -23322,7 +23340,7 @@
         <v>12</v>
       </c>
       <c r="C131" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="F131"/>
     </row>
@@ -23334,7 +23352,7 @@
         <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F132"/>
     </row>
@@ -23346,7 +23364,7 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="F133"/>
     </row>
@@ -23358,7 +23376,7 @@
         <v>12</v>
       </c>
       <c r="C134" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="F134"/>
     </row>
@@ -23370,7 +23388,7 @@
         <v>12</v>
       </c>
       <c r="C135" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="F135"/>
     </row>
@@ -23382,7 +23400,7 @@
         <v>12</v>
       </c>
       <c r="C136" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F136"/>
     </row>
@@ -23394,7 +23412,7 @@
         <v>12</v>
       </c>
       <c r="C137" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F137"/>
     </row>
@@ -23406,7 +23424,7 @@
         <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="F138"/>
     </row>
@@ -23418,7 +23436,7 @@
         <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F139"/>
     </row>
@@ -23430,7 +23448,7 @@
         <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F140"/>
     </row>
@@ -23442,7 +23460,7 @@
         <v>13</v>
       </c>
       <c r="C141" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="F141"/>
     </row>
@@ -23454,7 +23472,7 @@
         <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="F142"/>
     </row>
@@ -23466,7 +23484,7 @@
         <v>13</v>
       </c>
       <c r="C143" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="F143"/>
     </row>
@@ -23478,7 +23496,7 @@
         <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="F144"/>
     </row>
@@ -23490,7 +23508,7 @@
         <v>13</v>
       </c>
       <c r="C145" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F145"/>
     </row>
@@ -23502,7 +23520,7 @@
         <v>13</v>
       </c>
       <c r="C146" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F146"/>
     </row>
@@ -23514,7 +23532,7 @@
         <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F147"/>
     </row>
@@ -23526,7 +23544,7 @@
         <v>13</v>
       </c>
       <c r="C148" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F148"/>
     </row>
@@ -23538,7 +23556,7 @@
         <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="F149"/>
     </row>
@@ -23550,7 +23568,7 @@
         <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="F150"/>
     </row>
@@ -23562,7 +23580,7 @@
         <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="F151"/>
     </row>
@@ -23574,7 +23592,7 @@
         <v>13</v>
       </c>
       <c r="C152" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F152"/>
     </row>
@@ -23586,7 +23604,7 @@
         <v>13</v>
       </c>
       <c r="C153" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="F153"/>
     </row>
@@ -23598,7 +23616,7 @@
         <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F154"/>
     </row>
@@ -23610,7 +23628,7 @@
         <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F155"/>
     </row>
@@ -23622,7 +23640,7 @@
         <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="F156"/>
     </row>
@@ -23634,7 +23652,7 @@
         <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="F157"/>
     </row>
@@ -23646,7 +23664,7 @@
         <v>14</v>
       </c>
       <c r="C158" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="F158"/>
     </row>
@@ -23658,7 +23676,7 @@
         <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="F159"/>
     </row>
@@ -23670,7 +23688,7 @@
         <v>14</v>
       </c>
       <c r="C160" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F160"/>
     </row>
@@ -23682,7 +23700,7 @@
         <v>14</v>
       </c>
       <c r="C161" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="F161"/>
     </row>
@@ -23694,7 +23712,7 @@
         <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="F162"/>
     </row>
@@ -23706,7 +23724,7 @@
         <v>14</v>
       </c>
       <c r="C163" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F163"/>
     </row>
@@ -23718,7 +23736,7 @@
         <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F164"/>
     </row>
@@ -23730,7 +23748,7 @@
         <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F165"/>
     </row>
@@ -23742,7 +23760,7 @@
         <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="F166"/>
     </row>
@@ -23754,7 +23772,7 @@
         <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F167"/>
     </row>
@@ -23766,7 +23784,7 @@
         <v>14</v>
       </c>
       <c r="C168" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="F168"/>
     </row>
@@ -23778,7 +23796,7 @@
         <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="F169"/>
     </row>
@@ -23790,7 +23808,7 @@
         <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F170"/>
     </row>
@@ -23802,7 +23820,7 @@
         <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="F171"/>
     </row>
@@ -23814,7 +23832,7 @@
         <v>15</v>
       </c>
       <c r="C172" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F172"/>
     </row>
@@ -23826,7 +23844,7 @@
         <v>15</v>
       </c>
       <c r="C173" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F173"/>
     </row>
@@ -23838,7 +23856,7 @@
         <v>15</v>
       </c>
       <c r="C174" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="F174"/>
     </row>
@@ -23850,7 +23868,7 @@
         <v>15</v>
       </c>
       <c r="C175" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="F175"/>
     </row>
@@ -23862,7 +23880,7 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="F176"/>
     </row>
@@ -23874,7 +23892,7 @@
         <v>15</v>
       </c>
       <c r="C177" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="178">
@@ -23885,7 +23903,7 @@
         <v>15</v>
       </c>
       <c r="C178" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F178"/>
     </row>
@@ -23897,7 +23915,7 @@
         <v>15</v>
       </c>
       <c r="C179" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F179"/>
     </row>
@@ -23909,7 +23927,7 @@
         <v>15</v>
       </c>
       <c r="C180" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="181">
@@ -23920,7 +23938,7 @@
         <v>15</v>
       </c>
       <c r="C181" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="182">
@@ -23931,7 +23949,7 @@
         <v>15</v>
       </c>
       <c r="C182" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="183">
@@ -23942,7 +23960,7 @@
         <v>15</v>
       </c>
       <c r="C183" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="184">
@@ -23953,7 +23971,7 @@
         <v>15</v>
       </c>
       <c r="C184" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="185">
@@ -23964,7 +23982,7 @@
         <v>15</v>
       </c>
       <c r="C185" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="186">
@@ -23975,7 +23993,7 @@
         <v>15</v>
       </c>
       <c r="C186" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="187">
@@ -23986,7 +24004,7 @@
         <v>15</v>
       </c>
       <c r="C187" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="188">
@@ -23997,7 +24015,7 @@
         <v>15</v>
       </c>
       <c r="C188" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="189">
@@ -24008,7 +24026,7 @@
         <v>7</v>
       </c>
       <c r="C189" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="190">
@@ -24019,7 +24037,7 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="191">
@@ -24030,7 +24048,7 @@
         <v>9</v>
       </c>
       <c r="C191" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="192">
@@ -24041,7 +24059,7 @@
         <v>10</v>
       </c>
       <c r="C192" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="193">
@@ -24052,7 +24070,7 @@
         <v>11</v>
       </c>
       <c r="C193" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="194">
@@ -24063,7 +24081,7 @@
         <v>12</v>
       </c>
       <c r="C194" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="195">
@@ -24074,7 +24092,7 @@
         <v>13</v>
       </c>
       <c r="C195" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="196">
@@ -24085,7 +24103,7 @@
         <v>14</v>
       </c>
       <c r="C196" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="197">
@@ -24096,7 +24114,7 @@
         <v>15</v>
       </c>
       <c r="C197" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -24118,13 +24136,13 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C1" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D1" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2">
@@ -24138,7 +24156,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3">
@@ -24152,7 +24170,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4">
@@ -24166,7 +24184,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5">
@@ -24180,7 +24198,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6">
@@ -24194,7 +24212,7 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7">
@@ -24208,7 +24226,7 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -24516,7 +24534,7 @@
         <v>2103</v>
       </c>
       <c r="G22" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23">
@@ -24530,7 +24548,7 @@
         <v>2203</v>
       </c>
       <c r="G23" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24">
@@ -24544,7 +24562,7 @@
         <v>2303</v>
       </c>
       <c r="G24" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="25">
@@ -24558,7 +24576,7 @@
         <v>2403</v>
       </c>
       <c r="G25" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26">
@@ -24572,7 +24590,7 @@
         <v>2503</v>
       </c>
       <c r="G26" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="27">
@@ -24586,7 +24604,7 @@
         <v>2603</v>
       </c>
       <c r="G27" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28">
@@ -24600,7 +24618,7 @@
         <v>2703</v>
       </c>
       <c r="G28" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29">
@@ -24614,7 +24632,7 @@
         <v>2803</v>
       </c>
       <c r="G29" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="30">
@@ -24628,7 +24646,7 @@
         <v>2903</v>
       </c>
       <c r="G30" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
     </row>
     <row r="31">
@@ -24642,7 +24660,7 @@
         <v>3003</v>
       </c>
       <c r="G31" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="32">
@@ -24656,7 +24674,7 @@
         <v>3103</v>
       </c>
       <c r="G32" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="33">
@@ -24670,7 +24688,7 @@
         <v>3203</v>
       </c>
       <c r="G33" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="34">
@@ -24684,7 +24702,7 @@
         <v>3303</v>
       </c>
       <c r="G34" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="35">
@@ -24698,7 +24716,7 @@
         <v>3403</v>
       </c>
       <c r="G35" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="36">
@@ -24712,7 +24730,7 @@
         <v>3503</v>
       </c>
       <c r="G36" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="37">
@@ -24726,7 +24744,7 @@
         <v>3603</v>
       </c>
       <c r="G37" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="38">
@@ -24740,7 +24758,7 @@
         <v>3703</v>
       </c>
       <c r="G38" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="39">
@@ -24754,7 +24772,7 @@
         <v>3803</v>
       </c>
       <c r="G39" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="40">
@@ -24768,7 +24786,7 @@
         <v>3903</v>
       </c>
       <c r="G40" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="41">
@@ -24782,7 +24800,7 @@
         <v>4003</v>
       </c>
       <c r="G41" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="42">
@@ -24796,7 +24814,7 @@
         <v>4103</v>
       </c>
       <c r="G42" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="43">
@@ -24810,7 +24828,7 @@
         <v>4203</v>
       </c>
       <c r="G43" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="44">
@@ -24824,7 +24842,7 @@
         <v>4303</v>
       </c>
       <c r="G44" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="45">
@@ -24838,7 +24856,7 @@
         <v>4403</v>
       </c>
       <c r="G45" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="46">
@@ -24852,7 +24870,7 @@
         <v>4503</v>
       </c>
       <c r="G46" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="47">
@@ -24866,7 +24884,7 @@
         <v>4603</v>
       </c>
       <c r="G47" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="48">
@@ -24880,7 +24898,7 @@
         <v>4703</v>
       </c>
       <c r="G48" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="49">
@@ -24894,7 +24912,7 @@
         <v>4803</v>
       </c>
       <c r="G49" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="50">
@@ -24908,7 +24926,7 @@
         <v>4903</v>
       </c>
       <c r="G50" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="51">
@@ -24922,7 +24940,7 @@
         <v>5003</v>
       </c>
       <c r="G51" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="52">
@@ -24936,7 +24954,7 @@
         <v>5103</v>
       </c>
       <c r="G52" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
     </row>
     <row r="53">
@@ -24950,7 +24968,7 @@
         <v>5203</v>
       </c>
       <c r="G53" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="54">
@@ -24964,7 +24982,7 @@
         <v>5303</v>
       </c>
       <c r="G54" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
     <row r="55">
@@ -24978,7 +24996,7 @@
         <v>5403</v>
       </c>
       <c r="G55" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56">
@@ -24992,7 +25010,7 @@
         <v>5503</v>
       </c>
       <c r="G56" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
     </row>
     <row r="57">
@@ -25006,7 +25024,7 @@
         <v>5603</v>
       </c>
       <c r="G57" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="58">
@@ -25020,7 +25038,7 @@
         <v>5703</v>
       </c>
       <c r="G58" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="59">
@@ -25034,7 +25052,7 @@
         <v>5803</v>
       </c>
       <c r="G59" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="60">
@@ -25048,7 +25066,7 @@
         <v>5903</v>
       </c>
       <c r="G60" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
     </row>
     <row r="61">
@@ -25062,7 +25080,7 @@
         <v>6003</v>
       </c>
       <c r="G61" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="62">
@@ -25076,7 +25094,7 @@
         <v>6103</v>
       </c>
       <c r="G62" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="63">
@@ -25090,7 +25108,7 @@
         <v>6203</v>
       </c>
       <c r="G63" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="64">
@@ -25104,7 +25122,7 @@
         <v>6303</v>
       </c>
       <c r="G64" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="65">
@@ -25118,7 +25136,7 @@
         <v>6403</v>
       </c>
       <c r="G65" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="66">
@@ -25132,7 +25150,7 @@
         <v>6503</v>
       </c>
       <c r="G66" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="67">
@@ -25146,7 +25164,7 @@
         <v>6603</v>
       </c>
       <c r="G67" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="68">
@@ -25160,7 +25178,7 @@
         <v>6703</v>
       </c>
       <c r="G68" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="69">
@@ -25174,7 +25192,7 @@
         <v>6803</v>
       </c>
       <c r="G69" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="70">
@@ -25188,7 +25206,7 @@
         <v>6903</v>
       </c>
       <c r="G70" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="71">
@@ -25202,7 +25220,7 @@
         <v>7003</v>
       </c>
       <c r="G71" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
     </row>
     <row r="72">
@@ -25216,7 +25234,7 @@
         <v>7103</v>
       </c>
       <c r="G72" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="73">
@@ -25230,7 +25248,7 @@
         <v>7203</v>
       </c>
       <c r="G73" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="74">
@@ -25244,7 +25262,7 @@
         <v>7303</v>
       </c>
       <c r="G74" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="75">
@@ -25258,7 +25276,7 @@
         <v>7403</v>
       </c>
       <c r="G75" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
     </row>
     <row r="76">
@@ -25272,7 +25290,7 @@
         <v>7503</v>
       </c>
       <c r="G76" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="77">
@@ -25286,7 +25304,7 @@
         <v>7603</v>
       </c>
       <c r="G77" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
     </row>
     <row r="78">
@@ -25300,7 +25318,7 @@
         <v>7703</v>
       </c>
       <c r="G78" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="79">
@@ -25314,7 +25332,7 @@
         <v>7803</v>
       </c>
       <c r="G79" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="80">
@@ -25328,7 +25346,7 @@
         <v>7903</v>
       </c>
       <c r="G80" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="81">
@@ -25342,7 +25360,7 @@
         <v>8003</v>
       </c>
       <c r="G81" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="82">
@@ -25356,7 +25374,7 @@
         <v>8103</v>
       </c>
       <c r="G82" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="83">
@@ -25370,7 +25388,7 @@
         <v>8203</v>
       </c>
       <c r="G83" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="84">
@@ -25384,7 +25402,7 @@
         <v>8303</v>
       </c>
       <c r="G84" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
     </row>
     <row r="85">
@@ -25398,7 +25416,7 @@
         <v>8403</v>
       </c>
       <c r="G85" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="86">
@@ -25412,7 +25430,7 @@
         <v>8503</v>
       </c>
       <c r="G86" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="87">
@@ -25426,7 +25444,7 @@
         <v>8603</v>
       </c>
       <c r="G87" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="88">
@@ -25440,7 +25458,7 @@
         <v>8703</v>
       </c>
       <c r="G88" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="89">
@@ -25454,7 +25472,7 @@
         <v>8803</v>
       </c>
       <c r="G89" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="90">
@@ -25468,7 +25486,7 @@
         <v>8903</v>
       </c>
       <c r="G90" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
     </row>
     <row r="91">
@@ -25482,7 +25500,7 @@
         <v>9003</v>
       </c>
       <c r="G91" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
     <row r="92">
@@ -25496,7 +25514,7 @@
         <v>9103</v>
       </c>
       <c r="G92" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="93">
@@ -25510,7 +25528,7 @@
         <v>9203</v>
       </c>
       <c r="G93" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="94">
@@ -25524,7 +25542,7 @@
         <v>9303</v>
       </c>
       <c r="G94" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
     </row>
     <row r="95">
@@ -25538,7 +25556,7 @@
         <v>9403</v>
       </c>
       <c r="G95" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="96">
@@ -25552,7 +25570,7 @@
         <v>9503</v>
       </c>
       <c r="G96" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="97">
@@ -25566,7 +25584,7 @@
         <v>9603</v>
       </c>
       <c r="G97" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="98">
@@ -25580,7 +25598,7 @@
         <v>9703</v>
       </c>
       <c r="G98" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
     </row>
     <row r="99">
@@ -25594,7 +25612,7 @@
         <v>9803</v>
       </c>
       <c r="G99" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="100">
@@ -25608,7 +25626,7 @@
         <v>9903</v>
       </c>
       <c r="G100" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
     </row>
     <row r="101">
@@ -25622,7 +25640,7 @@
         <v>10003</v>
       </c>
       <c r="G101" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="102">
@@ -25636,7 +25654,7 @@
         <v>10103</v>
       </c>
       <c r="G102" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
     </row>
     <row r="103">
@@ -25650,7 +25668,7 @@
         <v>10203</v>
       </c>
       <c r="G103" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="104">
@@ -25664,7 +25682,7 @@
         <v>10303</v>
       </c>
       <c r="G104" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
     </row>
     <row r="105">
@@ -25678,7 +25696,7 @@
         <v>10403</v>
       </c>
       <c r="G105" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="106">
@@ -25692,7 +25710,7 @@
         <v>10503</v>
       </c>
       <c r="G106" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
     </row>
     <row r="107">
@@ -25706,7 +25724,7 @@
         <v>10603</v>
       </c>
       <c r="G107" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="108">
@@ -25720,7 +25738,7 @@
         <v>10703</v>
       </c>
       <c r="G108" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
     </row>
     <row r="109">
@@ -25734,7 +25752,7 @@
         <v>10803</v>
       </c>
       <c r="G109" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="110">
@@ -25748,7 +25766,7 @@
         <v>10903</v>
       </c>
       <c r="G110" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
     </row>
     <row r="111">
@@ -25762,7 +25780,7 @@
         <v>11003</v>
       </c>
       <c r="G111" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="112">
@@ -25776,7 +25794,7 @@
         <v>11103</v>
       </c>
       <c r="G112" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
     </row>
     <row r="113">
@@ -25790,7 +25808,7 @@
         <v>11203</v>
       </c>
       <c r="G113" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="114">
@@ -25804,7 +25822,7 @@
         <v>11303</v>
       </c>
       <c r="G114" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
     </row>
     <row r="115">
@@ -25818,7 +25836,7 @@
         <v>11403</v>
       </c>
       <c r="G115" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="116">
@@ -25832,7 +25850,7 @@
         <v>11503</v>
       </c>
       <c r="G116" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="117">
@@ -25846,7 +25864,7 @@
         <v>11603</v>
       </c>
       <c r="G117" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="118">
@@ -25860,7 +25878,7 @@
         <v>11703</v>
       </c>
       <c r="G118" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
     </row>
     <row r="119">
@@ -25874,7 +25892,7 @@
         <v>11803</v>
       </c>
       <c r="G119" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="120">
@@ -25888,7 +25906,7 @@
         <v>11903</v>
       </c>
       <c r="G120" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="121">
@@ -25902,7 +25920,7 @@
         <v>12003</v>
       </c>
       <c r="G121" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="122">
@@ -25916,7 +25934,7 @@
         <v>12103</v>
       </c>
       <c r="G122" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
     <row r="123">
@@ -25930,7 +25948,7 @@
         <v>12203</v>
       </c>
       <c r="G123" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="124">
@@ -25944,7 +25962,7 @@
         <v>12303</v>
       </c>
       <c r="G124" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="125">
@@ -25958,7 +25976,7 @@
         <v>12403</v>
       </c>
       <c r="G125" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="126">
@@ -25972,7 +25990,7 @@
         <v>12503</v>
       </c>
       <c r="G126" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
     </row>
     <row r="127">
@@ -25986,7 +26004,7 @@
         <v>12603</v>
       </c>
       <c r="G127" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="128">
@@ -26000,7 +26018,7 @@
         <v>12703</v>
       </c>
       <c r="G128" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="129">
@@ -26014,7 +26032,7 @@
         <v>12803</v>
       </c>
       <c r="G129" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="130">
@@ -26028,7 +26046,7 @@
         <v>12903</v>
       </c>
       <c r="G130" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="131">
@@ -26042,7 +26060,7 @@
         <v>13003</v>
       </c>
       <c r="G131" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
     </row>
     <row r="132">
@@ -26056,7 +26074,7 @@
         <v>13103</v>
       </c>
       <c r="G132" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="133">
@@ -26070,7 +26088,7 @@
         <v>13203</v>
       </c>
       <c r="G133" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="134">
@@ -26084,7 +26102,7 @@
         <v>13303</v>
       </c>
       <c r="G134" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="135">
@@ -26098,7 +26116,7 @@
         <v>13403</v>
       </c>
       <c r="G135" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="136">
@@ -26112,7 +26130,7 @@
         <v>13503</v>
       </c>
       <c r="G136" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="137">
@@ -26126,7 +26144,7 @@
         <v>13603</v>
       </c>
       <c r="G137" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="138">
@@ -26140,7 +26158,7 @@
         <v>13703</v>
       </c>
       <c r="G138" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="139">
@@ -26154,7 +26172,7 @@
         <v>13803</v>
       </c>
       <c r="G139" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="140">
@@ -26168,7 +26186,7 @@
         <v>13903</v>
       </c>
       <c r="G140" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="141">
@@ -26182,7 +26200,7 @@
         <v>14003</v>
       </c>
       <c r="G141" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="142">
@@ -26196,7 +26214,7 @@
         <v>14103</v>
       </c>
       <c r="G142" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="143">
@@ -26210,7 +26228,7 @@
         <v>14203</v>
       </c>
       <c r="G143" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
     </row>
     <row r="144">
@@ -26224,7 +26242,7 @@
         <v>14303</v>
       </c>
       <c r="G144" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="145">
@@ -26238,7 +26256,7 @@
         <v>14403</v>
       </c>
       <c r="G145" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="146">
@@ -26252,7 +26270,7 @@
         <v>14503</v>
       </c>
       <c r="G146" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="147">
@@ -26266,7 +26284,7 @@
         <v>14603</v>
       </c>
       <c r="G147" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="148">
@@ -26280,7 +26298,7 @@
         <v>14703</v>
       </c>
       <c r="G148" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="149">
@@ -26294,7 +26312,7 @@
         <v>14803</v>
       </c>
       <c r="G149" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="150">
@@ -26308,7 +26326,7 @@
         <v>14903</v>
       </c>
       <c r="G150" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
     <row r="151">
@@ -26322,7 +26340,7 @@
         <v>15003</v>
       </c>
       <c r="G151" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="152">
@@ -26336,7 +26354,7 @@
         <v>15103</v>
       </c>
       <c r="G152" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="153">
@@ -26350,7 +26368,7 @@
         <v>15203</v>
       </c>
       <c r="G153" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="154">
@@ -26364,7 +26382,7 @@
         <v>15303</v>
       </c>
       <c r="G154" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="155">
@@ -26378,7 +26396,7 @@
         <v>15403</v>
       </c>
       <c r="G155" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="156">
@@ -26392,7 +26410,7 @@
         <v>15503</v>
       </c>
       <c r="G156" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="157">
@@ -26406,7 +26424,7 @@
         <v>15603</v>
       </c>
       <c r="G157" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
     </row>
     <row r="158">
@@ -26420,7 +26438,7 @@
         <v>15703</v>
       </c>
       <c r="G158" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
     </row>
     <row r="159">
@@ -26434,7 +26452,7 @@
         <v>15803</v>
       </c>
       <c r="G159" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="160">
@@ -26448,7 +26466,7 @@
         <v>15903</v>
       </c>
       <c r="G160" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
     </row>
     <row r="161">
@@ -26462,7 +26480,7 @@
         <v>16003</v>
       </c>
       <c r="G161" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
     <row r="162">
@@ -26476,7 +26494,7 @@
         <v>16103</v>
       </c>
       <c r="G162" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
     </row>
     <row r="163">
@@ -26490,7 +26508,7 @@
         <v>16203</v>
       </c>
       <c r="G163" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
     </row>
     <row r="164">
@@ -26504,7 +26522,7 @@
         <v>16303</v>
       </c>
       <c r="G164" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
     </row>
     <row r="165">
@@ -26518,7 +26536,7 @@
         <v>16403</v>
       </c>
       <c r="G165" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
     </row>
     <row r="166">
@@ -26532,7 +26550,7 @@
         <v>16503</v>
       </c>
       <c r="G166" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
     </row>
     <row r="167">
@@ -26546,7 +26564,7 @@
         <v>16603</v>
       </c>
       <c r="G167" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="168">
@@ -26560,7 +26578,7 @@
         <v>16703</v>
       </c>
       <c r="G168" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
     </row>
     <row r="169">
@@ -26574,7 +26592,7 @@
         <v>16803</v>
       </c>
       <c r="G169" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
     </row>
     <row r="170">
@@ -26588,7 +26606,7 @@
         <v>16903</v>
       </c>
       <c r="G170" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="171">
@@ -26602,7 +26620,7 @@
         <v>17003</v>
       </c>
       <c r="G171" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="172">
@@ -26616,7 +26634,7 @@
         <v>17103</v>
       </c>
       <c r="G172" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
     </row>
     <row r="173">
@@ -26630,7 +26648,7 @@
         <v>17203</v>
       </c>
       <c r="G173" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
     </row>
     <row r="174">
@@ -26644,7 +26662,7 @@
         <v>17303</v>
       </c>
       <c r="G174" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="175">
@@ -26658,7 +26676,7 @@
         <v>17403</v>
       </c>
       <c r="G175" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
     </row>
     <row r="176">
@@ -26672,7 +26690,7 @@
         <v>17503</v>
       </c>
       <c r="G176" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
     </row>
     <row r="177">
@@ -26686,7 +26704,7 @@
         <v>17603</v>
       </c>
       <c r="G177" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
     </row>
     <row r="178">
@@ -26700,7 +26718,7 @@
         <v>17703</v>
       </c>
       <c r="G178" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
     </row>
     <row r="179">
@@ -26714,7 +26732,7 @@
         <v>17803</v>
       </c>
       <c r="G179" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
     </row>
     <row r="180">
@@ -26728,7 +26746,7 @@
         <v>17903</v>
       </c>
       <c r="G180" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="181">
@@ -26742,7 +26760,7 @@
         <v>18003</v>
       </c>
       <c r="G181" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
     </row>
     <row r="182">
@@ -26756,7 +26774,7 @@
         <v>18103</v>
       </c>
       <c r="G182" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
     </row>
     <row r="183">
@@ -26770,7 +26788,7 @@
         <v>18203</v>
       </c>
       <c r="G183" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
     <row r="184">
@@ -26784,7 +26802,7 @@
         <v>18303</v>
       </c>
       <c r="G184" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
     </row>
     <row r="185">
@@ -26798,7 +26816,7 @@
         <v>18403</v>
       </c>
       <c r="G185" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
     </row>
     <row r="186">
@@ -26812,7 +26830,7 @@
         <v>18503</v>
       </c>
       <c r="G186" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="187">
@@ -26826,7 +26844,7 @@
         <v>18603</v>
       </c>
       <c r="G187" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
     </row>
     <row r="188">
@@ -26840,7 +26858,7 @@
         <v>18703</v>
       </c>
       <c r="G188" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
     </row>
     <row r="189">
@@ -26854,7 +26872,7 @@
         <v>18803</v>
       </c>
       <c r="G189" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="190">
@@ -26868,7 +26886,7 @@
         <v>18903</v>
       </c>
       <c r="G190" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
     </row>
     <row r="191">
@@ -26882,7 +26900,7 @@
         <v>19003</v>
       </c>
       <c r="G191" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
     </row>
     <row r="192">
@@ -26896,7 +26914,7 @@
         <v>19103</v>
       </c>
       <c r="G192" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="193">
@@ -26910,7 +26928,7 @@
         <v>19203</v>
       </c>
       <c r="G193" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
     </row>
     <row r="194">
@@ -26924,7 +26942,7 @@
         <v>19303</v>
       </c>
       <c r="G194" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
     </row>
     <row r="195">
@@ -26938,7 +26956,7 @@
         <v>19403</v>
       </c>
       <c r="G195" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="196">
@@ -26952,7 +26970,7 @@
         <v>19503</v>
       </c>
       <c r="G196" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="197">
@@ -26966,7 +26984,7 @@
         <v>19603</v>
       </c>
       <c r="G197" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="198">
@@ -26980,7 +26998,7 @@
         <v>19703</v>
       </c>
       <c r="G198" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="199">
@@ -26994,7 +27012,7 @@
         <v>19803</v>
       </c>
       <c r="G199" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="200">
@@ -27008,7 +27026,7 @@
         <v>19903</v>
       </c>
       <c r="G200" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="201">
@@ -27022,7 +27040,7 @@
         <v>20003</v>
       </c>
       <c r="G201" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
     <row r="202">
@@ -27036,7 +27054,7 @@
         <v>20103</v>
       </c>
       <c r="G202" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="203">
@@ -27050,7 +27068,7 @@
         <v>20203</v>
       </c>
       <c r="G203" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="204">
@@ -27064,7 +27082,7 @@
         <v>20303</v>
       </c>
       <c r="G204" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="205">
@@ -27078,7 +27096,7 @@
         <v>20403</v>
       </c>
       <c r="G205" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="206">
@@ -27092,7 +27110,7 @@
         <v>20503</v>
       </c>
       <c r="G206" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
     </row>
     <row r="207">
@@ -27106,7 +27124,7 @@
         <v>20603</v>
       </c>
       <c r="G207" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="208">
@@ -27120,7 +27138,7 @@
         <v>20703</v>
       </c>
       <c r="G208" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
     </row>
     <row r="209">
@@ -27134,7 +27152,7 @@
         <v>20803</v>
       </c>
       <c r="G209" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
     </row>
     <row r="210">
@@ -27148,7 +27166,7 @@
         <v>20903</v>
       </c>
       <c r="G210" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
     </row>
     <row r="211">
@@ -27162,7 +27180,7 @@
         <v>21003</v>
       </c>
       <c r="G211" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="212">
@@ -27176,7 +27194,7 @@
         <v>21103</v>
       </c>
       <c r="G212" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
     </row>
     <row r="213">
@@ -27190,7 +27208,7 @@
         <v>21203</v>
       </c>
       <c r="G213" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="214">
@@ -27204,7 +27222,7 @@
         <v>21303</v>
       </c>
       <c r="G214" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
     </row>
     <row r="215">
@@ -27218,7 +27236,7 @@
         <v>21403</v>
       </c>
       <c r="G215" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="216">
@@ -27232,7 +27250,7 @@
         <v>21503</v>
       </c>
       <c r="G216" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
     </row>
     <row r="217">
@@ -27246,7 +27264,7 @@
         <v>21603</v>
       </c>
       <c r="G217" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
     </row>
     <row r="218">
@@ -27260,7 +27278,7 @@
         <v>21703</v>
       </c>
       <c r="G218" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="219">
@@ -27274,7 +27292,7 @@
         <v>21803</v>
       </c>
       <c r="G219" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
     </row>
     <row r="220">
@@ -27288,7 +27306,7 @@
         <v>21903</v>
       </c>
       <c r="G220" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
     </row>
     <row r="221">
@@ -27302,7 +27320,7 @@
         <v>22003</v>
       </c>
       <c r="G221" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="222">
@@ -27316,7 +27334,7 @@
         <v>22103</v>
       </c>
       <c r="G222" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
     </row>
     <row r="223">
@@ -27330,7 +27348,7 @@
         <v>22203</v>
       </c>
       <c r="G223" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
     </row>
     <row r="224">
@@ -27344,7 +27362,7 @@
         <v>22303</v>
       </c>
       <c r="G224" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="225">
@@ -27358,7 +27376,7 @@
         <v>22403</v>
       </c>
       <c r="G225" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="226">
@@ -27372,7 +27390,7 @@
         <v>22503</v>
       </c>
       <c r="G226" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
     </row>
     <row r="227">
@@ -27386,7 +27404,7 @@
         <v>22603</v>
       </c>
       <c r="G227" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="228">
@@ -27400,7 +27418,7 @@
         <v>22703</v>
       </c>
       <c r="G228" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
     </row>
     <row r="229">
@@ -27414,7 +27432,7 @@
         <v>22803</v>
       </c>
       <c r="G229" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
     </row>
     <row r="230">
@@ -27428,7 +27446,7 @@
         <v>22903</v>
       </c>
       <c r="G230" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
     </row>
     <row r="231">
@@ -27442,7 +27460,7 @@
         <v>23003</v>
       </c>
       <c r="G231" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="232">
@@ -27456,7 +27474,7 @@
         <v>23103</v>
       </c>
       <c r="G232" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
     </row>
     <row r="233">
@@ -27470,7 +27488,7 @@
         <v>23203</v>
       </c>
       <c r="G233" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
     </row>
     <row r="234">
@@ -27484,7 +27502,7 @@
         <v>23303</v>
       </c>
       <c r="G234" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
     </row>
     <row r="235">
@@ -27498,7 +27516,7 @@
         <v>23403</v>
       </c>
       <c r="G235" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
     </row>
     <row r="236">
@@ -27512,7 +27530,7 @@
         <v>23503</v>
       </c>
       <c r="G236" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
     </row>
     <row r="237">
@@ -27526,7 +27544,7 @@
         <v>23603</v>
       </c>
       <c r="G237" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
     </row>
     <row r="238">
@@ -27540,7 +27558,7 @@
         <v>23703</v>
       </c>
       <c r="G238" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
     </row>
     <row r="239">
@@ -27554,7 +27572,7 @@
         <v>23803</v>
       </c>
       <c r="G239" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
     </row>
     <row r="240">
@@ -27568,7 +27586,7 @@
         <v>23903</v>
       </c>
       <c r="G240" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
     </row>
     <row r="241">
@@ -27582,7 +27600,7 @@
         <v>24003</v>
       </c>
       <c r="G241" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="242">
@@ -27596,7 +27614,7 @@
         <v>24103</v>
       </c>
       <c r="G242" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
     </row>
     <row r="243">
@@ -27610,7 +27628,7 @@
         <v>24203</v>
       </c>
       <c r="G243" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
     </row>
     <row r="244">
@@ -27624,7 +27642,7 @@
         <v>24303</v>
       </c>
       <c r="G244" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
     </row>
     <row r="245">
@@ -27638,7 +27656,7 @@
         <v>24403</v>
       </c>
       <c r="G245" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
     </row>
     <row r="246">
@@ -27652,7 +27670,7 @@
         <v>24503</v>
       </c>
       <c r="G246" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
     </row>
     <row r="247">
@@ -27666,7 +27684,7 @@
         <v>24603</v>
       </c>
       <c r="G247" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
     </row>
     <row r="248">
@@ -27680,7 +27698,7 @@
         <v>24703</v>
       </c>
       <c r="G248" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
     </row>
     <row r="249">
@@ -27694,7 +27712,7 @@
         <v>24803</v>
       </c>
       <c r="G249" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
     </row>
     <row r="250">
@@ -27708,7 +27726,7 @@
         <v>24903</v>
       </c>
       <c r="G250" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
     </row>
     <row r="251">
@@ -27722,7 +27740,7 @@
         <v>25003</v>
       </c>
       <c r="G251" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
     </row>
     <row r="252">
@@ -27736,7 +27754,7 @@
         <v>25103</v>
       </c>
       <c r="G252" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
     </row>
     <row r="253">
@@ -27750,7 +27768,7 @@
         <v>25203</v>
       </c>
       <c r="G253" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="254">
@@ -27764,7 +27782,7 @@
         <v>25303</v>
       </c>
       <c r="G254" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
     </row>
     <row r="255">
@@ -27778,7 +27796,7 @@
         <v>25403</v>
       </c>
       <c r="G255" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
     </row>
     <row r="256">
@@ -27792,7 +27810,7 @@
         <v>25503</v>
       </c>
       <c r="G256" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
     </row>
     <row r="257">
@@ -27806,7 +27824,7 @@
         <v>25603</v>
       </c>
       <c r="G257" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="258">
@@ -27820,7 +27838,7 @@
         <v>25703</v>
       </c>
       <c r="G258" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
     </row>
     <row r="259">
@@ -27834,7 +27852,7 @@
         <v>25803</v>
       </c>
       <c r="G259" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
     </row>
     <row r="260">
@@ -27848,7 +27866,7 @@
         <v>25903</v>
       </c>
       <c r="G260" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
     </row>
     <row r="261">
@@ -27862,7 +27880,7 @@
         <v>26003</v>
       </c>
       <c r="G261" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
     </row>
     <row r="262">
@@ -27876,7 +27894,7 @@
         <v>26103</v>
       </c>
       <c r="G262" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
     </row>
     <row r="263">
@@ -27890,7 +27908,7 @@
         <v>26203</v>
       </c>
       <c r="G263" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
     </row>
     <row r="264">
@@ -27904,7 +27922,7 @@
         <v>26303</v>
       </c>
       <c r="G264" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
     </row>
     <row r="265">
@@ -27918,7 +27936,7 @@
         <v>26403</v>
       </c>
       <c r="G265" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
     </row>
     <row r="266">
@@ -27932,7 +27950,7 @@
         <v>26503</v>
       </c>
       <c r="G266" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
     </row>
     <row r="267">
@@ -27946,7 +27964,7 @@
         <v>26603</v>
       </c>
       <c r="G267" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
     </row>
     <row r="268">
@@ -27960,7 +27978,7 @@
         <v>26703</v>
       </c>
       <c r="G268" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
     </row>
     <row r="269">
@@ -27974,7 +27992,7 @@
         <v>26803</v>
       </c>
       <c r="G269" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
     </row>
     <row r="270">
@@ -27988,7 +28006,7 @@
         <v>26903</v>
       </c>
       <c r="G270" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
     </row>
     <row r="271">
@@ -28002,7 +28020,7 @@
         <v>27003</v>
       </c>
       <c r="G271" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
     </row>
     <row r="272">
@@ -28016,7 +28034,7 @@
         <v>27103</v>
       </c>
       <c r="G272" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
     </row>
     <row r="273">
@@ -28030,7 +28048,7 @@
         <v>27203</v>
       </c>
       <c r="G273" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
     </row>
     <row r="274">
@@ -28044,7 +28062,7 @@
         <v>27303</v>
       </c>
       <c r="G274" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
     </row>
     <row r="275">
@@ -28058,7 +28076,7 @@
         <v>27403</v>
       </c>
       <c r="G275" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
     </row>
     <row r="276">
@@ -28072,7 +28090,7 @@
         <v>27503</v>
       </c>
       <c r="G276" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
     </row>
     <row r="277">
@@ -28086,7 +28104,7 @@
         <v>27603</v>
       </c>
       <c r="G277" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="278">
@@ -28100,7 +28118,7 @@
         <v>27703</v>
       </c>
       <c r="G278" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
     </row>
     <row r="279">
@@ -28114,7 +28132,7 @@
         <v>27803</v>
       </c>
       <c r="G279" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="280">
@@ -28128,7 +28146,7 @@
         <v>27903</v>
       </c>
       <c r="G280" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
     </row>
     <row r="281">
@@ -28142,7 +28160,7 @@
         <v>28003</v>
       </c>
       <c r="G281" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
     </row>
     <row r="282">
@@ -28156,7 +28174,7 @@
         <v>28103</v>
       </c>
       <c r="G282" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
     </row>
     <row r="283">
@@ -28170,7 +28188,7 @@
         <v>28203</v>
       </c>
       <c r="G283" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
     </row>
     <row r="284">
@@ -28184,7 +28202,7 @@
         <v>28303</v>
       </c>
       <c r="G284" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
     </row>
     <row r="285">
@@ -28198,7 +28216,7 @@
         <v>28403</v>
       </c>
       <c r="G285" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
     </row>
     <row r="286">
@@ -28212,7 +28230,7 @@
         <v>28503</v>
       </c>
       <c r="G286" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
     </row>
     <row r="287">
@@ -28226,7 +28244,7 @@
         <v>28603</v>
       </c>
       <c r="G287" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
     </row>
     <row r="288">
@@ -28240,7 +28258,7 @@
         <v>28703</v>
       </c>
       <c r="G288" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
     </row>
     <row r="289">
@@ -28254,7 +28272,7 @@
         <v>28803</v>
       </c>
       <c r="G289" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
     </row>
     <row r="290">
@@ -28268,7 +28286,7 @@
         <v>28903</v>
       </c>
       <c r="G290" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
     </row>
     <row r="291">
@@ -28282,7 +28300,7 @@
         <v>29003</v>
       </c>
       <c r="G291" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
     </row>
     <row r="292">
@@ -28296,7 +28314,7 @@
         <v>29103</v>
       </c>
       <c r="G292" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
     </row>
     <row r="293">
@@ -28310,7 +28328,7 @@
         <v>29203</v>
       </c>
       <c r="G293" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
     </row>
     <row r="294">
@@ -28324,7 +28342,7 @@
         <v>29303</v>
       </c>
       <c r="G294" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
     </row>
     <row r="295">
@@ -28338,7 +28356,7 @@
         <v>29403</v>
       </c>
       <c r="G295" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
     </row>
     <row r="296">
@@ -28352,7 +28370,7 @@
         <v>29503</v>
       </c>
       <c r="G296" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
     </row>
     <row r="297">
@@ -28366,7 +28384,7 @@
         <v>29603</v>
       </c>
       <c r="G297" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
     </row>
     <row r="298">
@@ -28380,7 +28398,7 @@
         <v>29703</v>
       </c>
       <c r="G298" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
     </row>
     <row r="299">
@@ -28394,7 +28412,7 @@
         <v>29803</v>
       </c>
       <c r="G299" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
     </row>
     <row r="300">
@@ -28408,7 +28426,7 @@
         <v>29903</v>
       </c>
       <c r="G300" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
     </row>
     <row r="301">
@@ -28422,7 +28440,7 @@
         <v>30003</v>
       </c>
       <c r="G301" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
